--- a/data/Data Mentah.xlsx
+++ b/data/Data Mentah.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88596C2A-EAB5-4361-A167-618396607926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37FD472-767E-46C6-B696-BCEC11D5F669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="1650" windowWidth="21600" windowHeight="12645" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indeks Pembangunan Manusia" sheetId="2" r:id="rId1"/>
@@ -16091,7 +16091,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A3A2FD6-EC81-479F-9FA7-5D15615894AC}">
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -18360,6 +18360,24 @@
       </c>
       <c r="Q44">
         <v>76706.570000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K46">
+        <f>SUM(K4:K44)</f>
+        <v>3807879.2400000021</v>
+      </c>
+      <c r="L46">
+        <f>SUM(L4:L44)</f>
+        <v>3717394.2900000024</v>
+      </c>
+      <c r="M46">
+        <f>K46-L46</f>
+        <v>90484.949999999721</v>
+      </c>
+      <c r="N46">
+        <f>M46/K46</f>
+        <v>2.3762557659260136E-2</v>
       </c>
     </row>
   </sheetData>
